--- a/batch-2027-04.xlsx
+++ b/batch-2027-04.xlsx
@@ -587,12 +587,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2027-06-04</t>
+          <t>2027-08-02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2027-06-10</t>
+          <t>2027-08-06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -868,16 +868,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2027-06-04</t>
+          <t>2027-08-02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2027-06-10</t>
+          <t>2027-08-06</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/batch-2027-04.xlsx
+++ b/batch-2027-04.xlsx
@@ -587,12 +587,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2027-08-02</t>
+          <t>2027-06-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2027-08-06</t>
+          <t>2027-06-10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -868,16 +868,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2027-08-02</t>
+          <t>2027-06-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2027-08-06</t>
+          <t>2027-06-10</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
